--- a/public/templates/CITYBUS-BAO-CAO-HO-TRO-GSTT-BP-QLCL-DV.xlsx
+++ b/public/templates/CITYBUS-BAO-CAO-HO-TRO-GSTT-BP-QLCL-DV.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duykha/Documents/GSTT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duykha/Workspace/reactjs/qlcldv/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDCFDDD0-06B1-B748-872A-E1EC1B70D07A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05A94E6-0483-7F4B-916D-B294ED1C96EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>STT</t>
   </si>
@@ -70,15 +70,6 @@
   </si>
   <si>
     <t>Lý do Không thể khắc phục</t>
-  </si>
-  <si>
-    <t>HCM</t>
-  </si>
-  <si>
-    <t>(65) Bến Thành - CMT8 - Bến xe An Sương</t>
-  </si>
-  <si>
-    <t>50E61623</t>
   </si>
   <si>
     <r>
@@ -756,7 +747,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -793,7 +784,7 @@
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -863,18 +854,10 @@
       <c r="A8" s="6">
         <v>1</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="9">
-        <v>1</v>
-      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="7"/>
       <c r="H8" s="12"/>
@@ -889,7 +872,7 @@
       <c r="D9" s="15"/>
       <c r="E9" s="2">
         <f>SUM(E8:E8)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
         <f>SUM(F8:F8)</f>
